--- a/EXCEL/class notes/day7 vlookup/VlookupHlookup (Home work V1).xlsx
+++ b/EXCEL/class notes/day7 vlookup/VlookupHlookup (Home work V1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day7 vlookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4590D3-2748-4009-8413-957309FDA37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA550F1-5EFE-4E50-AA45-B7AC0A78C138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="797" xr2:uid="{5AAB12D2-2FD8-40D2-A0D7-860679C3315D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="797" activeTab="6" xr2:uid="{5AAB12D2-2FD8-40D2-A0D7-860679C3315D}"/>
   </bookViews>
   <sheets>
     <sheet name="Vlookup" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1150,12 +1159,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB75E5A-09F1-4660-85E5-EAFD714613AB}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="15" max="15" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1166,7 +1175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
         <v>1001</v>
       </c>
@@ -1189,7 +1198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -1200,7 +1209,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1003</v>
       </c>
@@ -1235,7 +1244,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1004</v>
       </c>
@@ -1274,7 +1283,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1005</v>
       </c>
@@ -1313,7 +1322,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1006</v>
       </c>
@@ -1346,7 +1355,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <v>1007</v>
       </c>
@@ -1379,7 +1388,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1008</v>
       </c>
@@ -1412,7 +1421,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1009</v>
       </c>
@@ -1445,7 +1454,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1010</v>
       </c>
@@ -1478,7 +1487,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F12" s="5">
         <v>1008</v>
       </c>
@@ -1502,7 +1511,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F13" s="5">
         <v>1004</v>
       </c>
@@ -1526,7 +1535,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F14" s="5">
         <v>1009</v>
       </c>
@@ -1550,7 +1559,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
@@ -1595,7 +1604,7 @@
         <v>A9</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>2</v>
       </c>
@@ -1640,7 +1649,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>0</v>
       </c>
@@ -1687,9 +1696,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552C1C32-7A52-47F0-9CA3-D0B893FEDF9B}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
@@ -1700,7 +1709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="41">
         <v>1001</v>
       </c>
@@ -1708,8 +1717,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="43">
-        <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F2" t="e">
         <f>MATCH(F$4,$B$1:$C$1,0)</f>
@@ -1724,7 +1732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="35">
         <v>1002</v>
       </c>
@@ -1732,11 +1740,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="36">
-        <f t="shared" ref="C3:C11" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="35">
         <v>1003</v>
       </c>
@@ -1744,8 +1751,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="37">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>0</v>
@@ -1766,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>1004</v>
       </c>
@@ -1774,25 +1780,30 @@
         <v>6</v>
       </c>
       <c r="C5" s="36">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E14" si="1">MATCH($F5,$A$1:$A$11,0)</f>
+        <f t="shared" ref="E5:E14" si="0">MATCH($F5,$A$1:$A$11,0)</f>
         <v>8</v>
       </c>
       <c r="F5" s="11">
         <v>1007</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="G5" s="7">
+        <f>VLOOKUP(F5,$A$1:$C$11,3,0)</f>
+        <v>24</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f>VLOOKUP(F5,$A$1:$C$11,2,0)</f>
+        <v>A7</v>
+      </c>
       <c r="J5" s="8"/>
       <c r="K5" s="3"/>
       <c r="L5" s="2">
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>1005</v>
       </c>
@@ -1800,25 +1811,30 @@
         <v>7</v>
       </c>
       <c r="C6" s="36">
-        <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F6" s="11">
         <v>1005</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="G6" s="7">
+        <f t="shared" ref="G6:G14" si="1">VLOOKUP(F6,$A$1:$C$11,3,0)</f>
+        <v>40</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f t="shared" ref="H6:H14" si="2">VLOOKUP(F6,$A$1:$C$11,2,0)</f>
+        <v>A5</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="2">
         <v>1005</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>1006</v>
       </c>
@@ -1826,25 +1842,30 @@
         <v>8</v>
       </c>
       <c r="C7" s="36">
-        <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="F7" s="11">
         <v>1006</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="G7" s="7">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A6</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="2">
         <v>1006</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>1007</v>
       </c>
@@ -1852,25 +1873,30 @@
         <v>9</v>
       </c>
       <c r="C8" s="36">
-        <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F8" s="11">
         <v>1002</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="G8" s="7">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A2</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="2">
         <v>1002</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>1008</v>
       </c>
@@ -1878,25 +1904,30 @@
         <v>10</v>
       </c>
       <c r="C9" s="36">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F9" s="11">
         <v>1003</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="G9" s="7">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A3</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="2">
         <v>1003</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>1009</v>
       </c>
@@ -1904,25 +1935,30 @@
         <v>11</v>
       </c>
       <c r="C10" s="36">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F10" s="11">
         <v>1010</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="G10" s="7">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A10</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="2">
         <v>1010</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="38">
         <v>1010</v>
       </c>
@@ -1930,73 +1966,96 @@
         <v>12</v>
       </c>
       <c r="C11" s="40">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F11" s="11">
         <v>1001</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="G11" s="7">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A1</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="2">
         <v>1001</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F12" s="11">
         <v>1008</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="7">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A8</v>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="2">
         <v>1008</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F13" s="11">
         <v>1004</v>
       </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="G13" s="7">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="H13" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A4</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="2">
         <v>1004</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F14" s="11">
         <v>1009</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="G14" s="7">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="H14" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A9</v>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="2">
         <v>1009</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F16" s="1" t="s">
         <v>0</v>
       </c>
@@ -2016,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F17" s="2">
         <v>1007</v>
       </c>
@@ -2028,7 +2087,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="18" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F18" s="2">
         <v>1005</v>
       </c>
@@ -2040,7 +2099,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="19" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F19" s="2">
         <v>1006</v>
       </c>
@@ -2052,7 +2111,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="20" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F20" s="2">
         <v>1002</v>
       </c>
@@ -2064,7 +2123,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="21" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F21" s="2">
         <v>1003</v>
       </c>
@@ -2076,7 +2135,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="22" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F22" s="2">
         <v>1010</v>
       </c>
@@ -2088,7 +2147,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="23" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F23" s="2">
         <v>1001</v>
       </c>
@@ -2100,7 +2159,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="24" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F24" s="2">
         <v>1008</v>
       </c>
@@ -2112,7 +2171,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="25" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F25" s="2">
         <v>1004</v>
       </c>
@@ -2124,7 +2183,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="26" spans="6:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F26" s="2">
         <v>1009</v>
       </c>
@@ -2144,13 +2203,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E531E5-42B1-48E6-A8CE-E2C2D14AC5FF}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2170,7 +2229,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
         <v>1001</v>
       </c>
@@ -2199,7 +2258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -2237,7 +2296,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1003</v>
       </c>
@@ -2276,7 +2335,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1004</v>
       </c>
@@ -2315,7 +2374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1005</v>
       </c>
@@ -2354,7 +2413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1006</v>
       </c>
@@ -2384,7 +2443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1007</v>
       </c>
@@ -2414,7 +2473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1008</v>
       </c>
@@ -2437,7 +2496,7 @@
         <v>B+</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1009</v>
       </c>
@@ -2460,7 +2519,7 @@
         <v>C+</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1010</v>
       </c>
@@ -2491,9 +2550,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA8E9C0-5CB8-48FB-8D5D-14BB7BBFEB50}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -2504,7 +2563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="21">
         <v>1001</v>
       </c>
@@ -2527,7 +2586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="16">
         <v>1002</v>
       </c>
@@ -2538,7 +2597,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="16">
         <v>1003</v>
       </c>
@@ -2567,7 +2626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="16">
         <v>1004</v>
       </c>
@@ -2600,7 +2659,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <v>1005</v>
       </c>
@@ -2633,7 +2692,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <v>1006</v>
       </c>
@@ -2666,7 +2725,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="16">
         <v>1007</v>
       </c>
@@ -2699,7 +2758,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <v>1008</v>
       </c>
@@ -2732,7 +2791,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="16">
         <v>1009</v>
       </c>
@@ -2765,7 +2824,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18">
         <v>1010</v>
       </c>
@@ -2798,7 +2857,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F12" s="2">
         <v>1008</v>
       </c>
@@ -2822,7 +2881,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F13" s="2">
         <v>1004</v>
       </c>
@@ -2846,7 +2905,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F14" s="2">
         <v>1009</v>
       </c>
@@ -2870,7 +2929,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
@@ -2915,7 +2974,7 @@
         <v>Nme9</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>2</v>
       </c>
@@ -2960,7 +3019,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>0</v>
       </c>
@@ -3004,9 +3063,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D77EA9-FF7E-4F08-9F7B-F82DEE8616C2}">
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
@@ -3044,7 +3103,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
@@ -3082,52 +3141,52 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="57" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="54">
         <f t="shared" ref="B3:K3" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C3" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D3" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E3" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F3" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G3" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H3" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="I3" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J3" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="K3" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G5" s="1" t="s">
         <v>0</v>
       </c>
@@ -3147,7 +3206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G6" s="5">
         <v>1007</v>
       </c>
@@ -3157,11 +3216,11 @@
       </c>
       <c r="I6" s="31">
         <f ca="1">HLOOKUP($G6,$A$1:$K$3,3,0)</f>
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="L6" s="27">
         <f ca="1">HLOOKUP($N6,$A$1:$K$3,MATCH(L$5,$A$1:$A$3,0),0)</f>
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M6" s="27" t="str">
         <f>HLOOKUP($N6,$A$1:$K$3,MATCH(M$5,$A$1:$A$3,0),0)</f>
@@ -3171,21 +3230,21 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G7" s="5">
         <v>1005</v>
       </c>
       <c r="H7" s="31" t="str">
-        <f t="shared" ref="H7:I15" si="1">HLOOKUP($G7,$A$1:$K$3,2,0)</f>
+        <f t="shared" ref="H7:H15" si="1">HLOOKUP($G7,$A$1:$K$3,2,0)</f>
         <v>A5</v>
       </c>
       <c r="I7" s="31">
         <f t="shared" ref="I7:I15" ca="1" si="2">HLOOKUP($G7,$A$1:$K$3,3,0)</f>
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="L7" s="27">
         <f t="shared" ref="L7:M15" ca="1" si="3">HLOOKUP($N7,$A$1:$K$3,MATCH(L$5,$A$1:$A$3,0),0)</f>
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="M7" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3198,7 +3257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G8" s="5">
         <v>1006</v>
       </c>
@@ -3208,11 +3267,11 @@
       </c>
       <c r="I8" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L8" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M8" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3234,7 +3293,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G9" s="5">
         <v>1002</v>
       </c>
@@ -3244,11 +3303,11 @@
       </c>
       <c r="I9" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L9" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M9" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3267,7 +3326,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G10" s="5">
         <v>1003</v>
       </c>
@@ -3277,11 +3336,11 @@
       </c>
       <c r="I10" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="L10" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="M10" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3300,7 +3359,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G11" s="5">
         <v>1010</v>
       </c>
@@ -3310,11 +3369,11 @@
       </c>
       <c r="I11" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L11" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="M11" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3333,7 +3392,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G12" s="5">
         <v>1001</v>
       </c>
@@ -3343,11 +3402,11 @@
       </c>
       <c r="I12" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L12" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M12" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3366,7 +3425,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G13" s="5">
         <v>1008</v>
       </c>
@@ -3376,11 +3435,11 @@
       </c>
       <c r="I13" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L13" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M13" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3390,7 +3449,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G14" s="5">
         <v>1004</v>
       </c>
@@ -3400,11 +3459,11 @@
       </c>
       <c r="I14" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L14" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M14" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3414,7 +3473,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="G15" s="5">
         <v>1009</v>
       </c>
@@ -3424,11 +3483,11 @@
       </c>
       <c r="I15" s="31">
         <f t="shared" ca="1" si="2"/>
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="L15" s="27">
         <f t="shared" ca="1" si="3"/>
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="M15" s="27" t="str">
         <f t="shared" si="3"/>
@@ -3438,7 +3497,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
         <v>1</v>
       </c>
@@ -3483,52 +3542,52 @@
         <v>A9</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="3">
         <f ca="1">HLOOKUP(D$19,$A$1:$K$3,MATCH($C18,$A$1:$A$3,0),0)</f>
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
         <v>0</v>
       </c>
@@ -3571,9 +3630,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0DD719-C09B-4C51-B019-B63D0233207F}">
   <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -3608,52 +3667,52 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4">
         <f t="shared" ref="B2:K2" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="D2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="K2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -3688,7 +3747,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
@@ -3726,7 +3785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C7" s="5">
         <v>1007</v>
       </c>
@@ -3736,7 +3795,7 @@
       </c>
       <c r="E7" s="3">
         <f ca="1">INDEX($A$1:$K$3,MATCH(E$6,$A$1:$A$3,0),MATCH($C7,$A$3:$K$3,0))</f>
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="G7" s="5">
         <v>1007</v>
@@ -3747,7 +3806,7 @@
       </c>
       <c r="I7" s="3">
         <f ca="1">INDEX($A$1:$K$3,2,MATCH($G7,$A$3:$K$3,0))</f>
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="L7" s="5">
         <v>1007</v>
@@ -3758,7 +3817,7 @@
       </c>
       <c r="N7" s="8">
         <f ca="1">INDEX($A$1:$K$3,MATCH(N$6,$A$1:$A$3,0),MATCH($L7,$A$3:$K$3,0))</f>
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="P7" s="5">
         <v>1007</v>
@@ -3766,7 +3825,7 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C8" s="5">
         <v>1005</v>
       </c>
@@ -3776,7 +3835,7 @@
       </c>
       <c r="E8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5">
         <v>1005</v>
@@ -3787,7 +3846,7 @@
       </c>
       <c r="I8" s="3">
         <f t="shared" ref="I8:I16" ca="1" si="3">INDEX($A$1:$K$3,2,MATCH($G8,$A$3:$K$3,0))</f>
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="L8" s="5">
         <v>1005</v>
@@ -3798,7 +3857,7 @@
       </c>
       <c r="N8" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="P8" s="5">
         <v>1005</v>
@@ -3806,7 +3865,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C9" s="5">
         <v>1006</v>
       </c>
@@ -3816,7 +3875,7 @@
       </c>
       <c r="E9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G9" s="5">
         <v>1006</v>
@@ -3827,7 +3886,7 @@
       </c>
       <c r="I9" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="L9" s="5">
         <v>1006</v>
@@ -3838,7 +3897,7 @@
       </c>
       <c r="N9" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="P9" s="5">
         <v>1006</v>
@@ -3846,7 +3905,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C10" s="5">
         <v>1002</v>
       </c>
@@ -3856,7 +3915,7 @@
       </c>
       <c r="E10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G10" s="5">
         <v>1002</v>
@@ -3867,7 +3926,7 @@
       </c>
       <c r="I10" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="L10" s="5">
         <v>1002</v>
@@ -3878,7 +3937,7 @@
       </c>
       <c r="N10" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P10" s="5">
         <v>1002</v>
@@ -3886,7 +3945,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C11" s="5">
         <v>1003</v>
       </c>
@@ -3896,7 +3955,7 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G11" s="5">
         <v>1003</v>
@@ -3907,7 +3966,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="L11" s="5">
         <v>1003</v>
@@ -3918,7 +3977,7 @@
       </c>
       <c r="N11" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="P11" s="5">
         <v>1003</v>
@@ -3926,7 +3985,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C12" s="5">
         <v>1010</v>
       </c>
@@ -3936,7 +3995,7 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G12" s="5">
         <v>1010</v>
@@ -3947,7 +4006,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="L12" s="5">
         <v>1010</v>
@@ -3958,7 +4017,7 @@
       </c>
       <c r="N12" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="P12" s="5">
         <v>1010</v>
@@ -3966,7 +4025,7 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C13" s="5">
         <v>1001</v>
       </c>
@@ -3976,7 +4035,7 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="G13" s="5">
         <v>1001</v>
@@ -3987,7 +4046,7 @@
       </c>
       <c r="I13" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="L13" s="5">
         <v>1001</v>
@@ -3998,7 +4057,7 @@
       </c>
       <c r="N13" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="P13" s="5">
         <v>1001</v>
@@ -4006,7 +4065,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C14" s="5">
         <v>1008</v>
       </c>
@@ -4016,7 +4075,7 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G14" s="5">
         <v>1008</v>
@@ -4027,7 +4086,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="L14" s="5">
         <v>1008</v>
@@ -4038,7 +4097,7 @@
       </c>
       <c r="N14" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="P14" s="5">
         <v>1008</v>
@@ -4046,7 +4105,7 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C15" s="5">
         <v>1004</v>
       </c>
@@ -4056,7 +4115,7 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="G15" s="5">
         <v>1004</v>
@@ -4067,7 +4126,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="L15" s="5">
         <v>1004</v>
@@ -4078,7 +4137,7 @@
       </c>
       <c r="N15" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="P15" s="5">
         <v>1004</v>
@@ -4086,7 +4145,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C16" s="5">
         <v>1009</v>
       </c>
@@ -4096,7 +4155,7 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="G16" s="5">
         <v>1009</v>
@@ -4107,7 +4166,7 @@
       </c>
       <c r="I16" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="L16" s="5">
         <v>1009</v>
@@ -4118,7 +4177,7 @@
       </c>
       <c r="N16" s="8">
         <f t="shared" ca="1" si="4"/>
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="P16" s="5">
         <v>1009</v>
@@ -4134,13 +4193,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2FE955-A310-4397-9790-B452809F5D0C}">
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="58"/>
+    <col min="1" max="16384" width="8.77734375" style="58"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="58">
         <v>1</v>
       </c>
@@ -4154,7 +4213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="58">
         <v>2</v>
       </c>
@@ -4163,13 +4222,13 @@
       </c>
       <c r="C3" s="63">
         <f t="shared" ref="C3:C12" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D3" s="64">
         <v>1001</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="58">
         <v>3</v>
       </c>
@@ -4195,19 +4254,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B5" s="65" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D5" s="67">
         <v>1003</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" s="65" t="s">
         <v>6</v>
       </c>
@@ -4258,13 +4317,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B7" s="65" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D7" s="67">
         <v>1005</v>
@@ -4282,7 +4341,7 @@
       </c>
       <c r="J7" s="76">
         <f ca="1">INDEX($B$2:$D$12,$F7,J$4)</f>
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="L7" s="69">
         <v>1007</v>
@@ -4293,7 +4352,7 @@
       </c>
       <c r="N7" s="71">
         <f ca="1">INDEX($B$2:$D$12,MATCH($L7,$D$2:$D$12,0),MATCH(N$6,$B$2:$D$2,0))</f>
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="69">
         <v>1007</v>
@@ -4306,13 +4365,13 @@
       <c r="V7" s="70"/>
       <c r="W7" s="71"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B8" s="65" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="D8" s="67">
         <v>1006</v>
@@ -4330,7 +4389,7 @@
       </c>
       <c r="J8" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L8" s="69">
         <v>1005</v>
@@ -4341,7 +4400,7 @@
       </c>
       <c r="N8" s="71">
         <f t="shared" ca="1" si="4"/>
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Q8" s="69">
         <v>1005</v>
@@ -4354,13 +4413,13 @@
       <c r="V8" s="71"/>
       <c r="W8" s="71"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B9" s="72" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D9" s="67">
         <v>1007</v>
@@ -4378,7 +4437,7 @@
       </c>
       <c r="J9" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="L9" s="69">
         <v>1006</v>
@@ -4389,7 +4448,7 @@
       </c>
       <c r="N9" s="71">
         <f t="shared" ca="1" si="4"/>
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="Q9" s="69">
         <v>1006</v>
@@ -4402,13 +4461,13 @@
       <c r="V9" s="71"/>
       <c r="W9" s="71"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B10" s="65" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D10" s="67">
         <v>1008</v>
@@ -4450,13 +4509,13 @@
       <c r="V10" s="71"/>
       <c r="W10" s="71"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B11" s="65" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D11" s="67">
         <v>1009</v>
@@ -4474,7 +4533,7 @@
       </c>
       <c r="J11" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L11" s="69">
         <v>1003</v>
@@ -4485,7 +4544,7 @@
       </c>
       <c r="N11" s="71">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="Q11" s="69">
         <v>1003</v>
@@ -4498,13 +4557,13 @@
       <c r="V11" s="71"/>
       <c r="W11" s="71"/>
     </row>
-    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="73" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="D12" s="75">
         <v>1010</v>
@@ -4522,7 +4581,7 @@
       </c>
       <c r="J12" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="L12" s="69">
         <v>1010</v>
@@ -4533,7 +4592,7 @@
       </c>
       <c r="N12" s="71">
         <f t="shared" ca="1" si="4"/>
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="69">
         <v>1010</v>
@@ -4546,7 +4605,7 @@
       <c r="V12" s="71"/>
       <c r="W12" s="71"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="F13" s="58">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -4560,7 +4619,7 @@
       </c>
       <c r="J13" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L13" s="69">
         <v>1001</v>
@@ -4571,7 +4630,7 @@
       </c>
       <c r="N13" s="71">
         <f t="shared" ca="1" si="4"/>
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="Q13" s="69">
         <v>1001</v>
@@ -4584,7 +4643,7 @@
       <c r="V13" s="71"/>
       <c r="W13" s="71"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B14" s="58" t="s">
         <v>66</v>
       </c>
@@ -4601,7 +4660,7 @@
       </c>
       <c r="J14" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L14" s="69">
         <v>1008</v>
@@ -4612,7 +4671,7 @@
       </c>
       <c r="N14" s="71">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="69">
         <v>1008</v>
@@ -4625,7 +4684,7 @@
       <c r="V14" s="71"/>
       <c r="W14" s="71"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B15" s="58" t="s">
         <v>49</v>
       </c>
@@ -4669,7 +4728,7 @@
       <c r="V15" s="71"/>
       <c r="W15" s="71"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B16" s="58" t="s">
         <v>51</v>
       </c>
@@ -4689,7 +4748,7 @@
       </c>
       <c r="J16" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="L16" s="69">
         <v>1009</v>
@@ -4700,7 +4759,7 @@
       </c>
       <c r="N16" s="71">
         <f t="shared" ca="1" si="4"/>
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="69">
         <v>1009</v>
@@ -4713,7 +4772,7 @@
       <c r="V16" s="71"/>
       <c r="W16" s="71"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="58" t="s">
         <v>52</v>
       </c>
@@ -4721,7 +4780,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="58" t="s">
         <v>53</v>
       </c>
@@ -4729,7 +4788,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="58" t="s">
         <v>54</v>
       </c>
@@ -4737,7 +4796,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="58" t="s">
         <v>55</v>
       </c>
@@ -4745,7 +4804,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="58" t="s">
         <v>56</v>
       </c>
@@ -4753,7 +4812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="58" t="s">
         <v>64</v>
       </c>
@@ -4761,7 +4820,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="58" t="s">
         <v>65</v>
       </c>
